--- a/tests/Browser/Excel/NghiQuyetBanHanh.xlsx
+++ b/tests/Browser/Excel/NghiQuyetBanHanh.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\TuDongLamViec\tests\Browser\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7439F7D-C972-48B8-A77E-5FF75B2C055C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79EB9F0-589F-496E-B422-A8E183A36A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{06A80A3C-E8BE-424B-9614-FA41F15A8077}"/>
+    <workbookView xWindow="3640" yWindow="2490" windowWidth="19200" windowHeight="10060" xr2:uid="{06A80A3C-E8BE-424B-9614-FA41F15A8077}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="36">
   <si>
     <t>ten_cuoc_hop</t>
   </si>
@@ -36,9 +36,6 @@
     <t>mo_ta</t>
   </si>
   <si>
-    <t>Cuộc họp A (24/8/2026)</t>
-  </si>
-  <si>
     <t>so_nghi_quyet</t>
   </si>
   <si>
@@ -60,15 +57,9 @@
     <t>files</t>
   </si>
   <si>
-    <t>mot_phan|toan_phan</t>
-  </si>
-  <si>
     <t>NQ2</t>
   </si>
   <si>
-    <t>Nghị quyết thêm tự động</t>
-  </si>
-  <si>
     <t>NQ3</t>
   </si>
   <si>
@@ -78,19 +69,70 @@
     <t>NQ5</t>
   </si>
   <si>
-    <t>NQ2|NQ2</t>
-  </si>
-  <si>
-    <t>NQ3|NQ3</t>
-  </si>
-  <si>
-    <t>Thay thế NQ2 lần 1|Thay thế NQ2 lần 2</t>
-  </si>
-  <si>
-    <t>Thay thế NQ3 lần 1|Thay thế NQ3 lần 2</t>
-  </si>
-  <si>
     <t>tailieu1.pdf|tailieu2.pdf</t>
+  </si>
+  <si>
+    <t>NQ6</t>
+  </si>
+  <si>
+    <t>NQ7</t>
+  </si>
+  <si>
+    <t>NQ8</t>
+  </si>
+  <si>
+    <t>NQ9</t>
+  </si>
+  <si>
+    <t>NQ10</t>
+  </si>
+  <si>
+    <t>Cuộc họp tỉnh 14/9/2026</t>
+  </si>
+  <si>
+    <t>mot_phan</t>
+  </si>
+  <si>
+    <t>tailieu1.pdf</t>
+  </si>
+  <si>
+    <t>Thay thế NQ2 một phần</t>
+  </si>
+  <si>
+    <t>Thay thế NQ3 toàn phần</t>
+  </si>
+  <si>
+    <t>toan_phan</t>
+  </si>
+  <si>
+    <t>tailieu2.pdf</t>
+  </si>
+  <si>
+    <t>Nghị quyết số 2</t>
+  </si>
+  <si>
+    <t>Nghị quyết số 3</t>
+  </si>
+  <si>
+    <t>Nghị quyết số 4</t>
+  </si>
+  <si>
+    <t>Nghị quyết số 5</t>
+  </si>
+  <si>
+    <t>Nghị quyết số 6</t>
+  </si>
+  <si>
+    <t>Nghị quyết số 7</t>
+  </si>
+  <si>
+    <t>Nghị quyết số 8</t>
+  </si>
+  <si>
+    <t>Nghị quyết số 9</t>
+  </si>
+  <si>
+    <t>Nghị quyết số 10</t>
   </si>
 </sst>
 </file>
@@ -468,7 +510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{521E990C-44C3-4D53-942C-AE6C6FB0D600}">
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.6328125" customWidth="1"/>
@@ -489,41 +531,41 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3">
         <v>46274</v>
@@ -535,23 +577,23 @@
         <v>46387</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3">
         <v>46274</v>
@@ -563,23 +605,23 @@
         <v>46387</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
     <row r="4" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C4" s="3">
         <v>46274</v>
@@ -591,29 +633,29 @@
         <v>46387</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
     </row>
     <row r="5" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C5" s="3">
         <v>46274</v>
@@ -625,99 +667,169 @@
         <v>46387</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A6" s="2"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
+    <row r="6" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="3">
+        <v>46275</v>
+      </c>
+      <c r="D6" s="3">
+        <v>46276</v>
+      </c>
+      <c r="E6" s="3">
+        <v>46387</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
+      <c r="J6" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A7" s="2"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+    <row r="7" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="3">
+        <v>46276</v>
+      </c>
+      <c r="D7" s="3">
+        <v>46277</v>
+      </c>
+      <c r="E7" s="3">
+        <v>46387</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
+      <c r="J7" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A8" s="2"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
+    <row r="8" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="3">
+        <v>46277</v>
+      </c>
+      <c r="D8" s="3">
+        <v>46278</v>
+      </c>
+      <c r="E8" s="3">
+        <v>46387</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
+      <c r="J8" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A9" s="2"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
+    <row r="9" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="3">
+        <v>46278</v>
+      </c>
+      <c r="D9" s="3">
+        <v>46279</v>
+      </c>
+      <c r="E9" s="3">
+        <v>46387</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
+      <c r="J9" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A10" s="2"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
+    <row r="10" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="3">
+        <v>46279</v>
+      </c>
+      <c r="D10" s="3">
+        <v>46280</v>
+      </c>
+      <c r="E10" s="3">
+        <v>46387</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
+      <c r="J10" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="2"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="3"/>
       <c r="D11" s="3"/>
-      <c r="E11" s="2"/>
+      <c r="E11" s="3"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
@@ -728,39 +840,51 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="2"/>
-      <c r="C12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="3"/>
       <c r="D12" s="3"/>
-      <c r="E12" s="2"/>
+      <c r="E12" s="3"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="2"/>
-      <c r="C13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="3"/>
       <c r="D13" s="3"/>
-      <c r="E13" s="2"/>
+      <c r="E13" s="3"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" s="2"/>
-      <c r="C14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="3"/>
       <c r="D14" s="3"/>
-      <c r="E14" s="2"/>
+      <c r="E14" s="3"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="2"/>
@@ -774,53 +898,125 @@
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="2"/>
-      <c r="C17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="3"/>
       <c r="D17" s="3"/>
-      <c r="E17" s="2"/>
+      <c r="E17" s="3"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="2"/>
-      <c r="C18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="3"/>
       <c r="D18" s="3"/>
-      <c r="E18" s="2"/>
+      <c r="E18" s="3"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="2"/>
-      <c r="C19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="3"/>
       <c r="D19" s="3"/>
-      <c r="E19" s="2"/>
+      <c r="E19" s="3"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="2"/>
-      <c r="C20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="3"/>
       <c r="D20" s="3"/>
-      <c r="E20" s="2"/>
+      <c r="E20" s="3"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="2"/>
-      <c r="C21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="3"/>
       <c r="D21" s="3"/>
-      <c r="E21" s="2"/>
+      <c r="E21" s="3"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="2"/>
-      <c r="C22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="3"/>
       <c r="D22" s="3"/>
-      <c r="E22" s="2"/>
+      <c r="E22" s="3"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
